--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5168237</t>
+          <t xml:space="preserve">306221, 306222, 306223, 306224, 306225, 306229, 306226, 306227, 306228</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>2048</v>
+        <v>8548</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171828</t>
+          <t xml:space="preserve">306720, 306722, 306721, 306723</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>532</v>
+        <v>6786</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181377</t>
+          <t xml:space="preserve">308624, 308625</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>806</v>
+        <v>2356</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181676</t>
+          <t xml:space="preserve">308625</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F8">
-        <v>814</v>
+        <v>2006</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181676</t>
+          <t xml:space="preserve">308625</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F9">
-        <v>1474</v>
+        <v>421</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181676</t>
+          <t xml:space="preserve">5171828</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F10">
-        <v>3164</v>
+        <v>532</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188218</t>
+          <t xml:space="preserve">5181377</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F11">
-        <v>497</v>
+        <v>806</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188218</t>
+          <t xml:space="preserve">5181676</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F12">
-        <v>372</v>
+        <v>814</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188474</t>
+          <t xml:space="preserve">5181676</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F13">
-        <v>584</v>
+        <v>1474</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189044</t>
+          <t xml:space="preserve">5181676</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F14">
-        <v>663</v>
+        <v>3164</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189069</t>
+          <t xml:space="preserve">5188218</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>1656</v>
+        <v>497</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189188</t>
+          <t xml:space="preserve">5188218</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>425</v>
+        <v>372</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193446</t>
+          <t xml:space="preserve">5188474</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F17">
-        <v>630</v>
+        <v>584</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5760218</t>
+          <t xml:space="preserve">5189044</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>392</v>
+        <v>663</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5760988</t>
+          <t xml:space="preserve">5189069</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F19">
-        <v>273</v>
+        <v>1656</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5761917</t>
+          <t xml:space="preserve">5189188</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>1477</v>
+        <v>425</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762441</t>
+          <t xml:space="preserve">5193446</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F21">
-        <v>1733</v>
+        <v>630</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762992</t>
+          <t xml:space="preserve">5760218</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>611</v>
+        <v>392</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763342</t>
+          <t xml:space="preserve">5760988</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F23">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763874</t>
+          <t xml:space="preserve">5761917</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>1495</v>
+        <v>1477</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764377</t>
+          <t xml:space="preserve">5762441</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F25">
-        <v>7525</v>
+        <v>1733</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764519</t>
+          <t xml:space="preserve">5762992</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F26">
-        <v>2651</v>
+        <v>611</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766142</t>
+          <t xml:space="preserve">5763342</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F27">
-        <v>1545</v>
+        <v>291</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766303</t>
+          <t xml:space="preserve">5764377</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="F28">
-        <v>1248</v>
+        <v>7525</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766667</t>
+          <t xml:space="preserve">5764519</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>274</v>
+        <v>2651</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7130187</t>
+          <t xml:space="preserve">5766303</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>283</v>
+        <v>1248</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">734426, 5182334</t>
+          <t xml:space="preserve">5766667</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F31">
-        <v>388</v>
+        <v>274</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">734453, 5764861</t>
+          <t xml:space="preserve">7130187</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>600</v>
+        <v>283</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">734570, 5763051</t>
+          <t xml:space="preserve">734426, 5182334</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F33">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">734655, 5765780</t>
+          <t xml:space="preserve">734453, 5764861</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>417</v>
+        <v>600</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">734667, 5764599</t>
+          <t xml:space="preserve">734570, 5763051</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>1775</v>
+        <v>425</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">734677, 5764684</t>
+          <t xml:space="preserve">734655, 5765780</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F36">
-        <v>336</v>
+        <v>417</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">734690, 5177090</t>
+          <t xml:space="preserve">734667, 5764599</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F37">
-        <v>571</v>
+        <v>1775</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">734787, 5194083</t>
+          <t xml:space="preserve">734677, 5764684</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F38">
-        <v>576</v>
+        <v>336</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">734985, 100055830</t>
+          <t xml:space="preserve">734690, 5177090</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>653</v>
+        <v>571</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">735009, 5186659</t>
+          <t xml:space="preserve">734787, 5194083</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>1161</v>
+        <v>576</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">735045, 1809456</t>
+          <t xml:space="preserve">734985, 100055830</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F41">
-        <v>1573</v>
+        <v>653</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8473404</t>
+          <t xml:space="preserve">735009, 5186659</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>358</v>
+        <v>1161</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589217</t>
+          <t xml:space="preserve">735045, 1809456</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>869</v>
+        <v>1573</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">8473404</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44">
-        <v>560</v>
+        <v>358</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">8589217</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F45">
-        <v>560</v>
+        <v>869</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F46">
-        <v>1283</v>
+        <v>560</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118463</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F47">
-        <v>594</v>
+        <v>560</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254128</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F48">
-        <v>274</v>
+        <v>1283</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9583353</t>
+          <t xml:space="preserve">9118463</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9583353</t>
+          <t xml:space="preserve">9254128</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>621</v>
+        <v>274</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9744778</t>
+          <t xml:space="preserve">9583353</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>340</v>
+        <v>585</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844795</t>
+          <t xml:space="preserve">9583353</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F52">
-        <v>348</v>
+        <v>621</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,30 +2631,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">7358819</t>
+          <t xml:space="preserve">9744778</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F53">
-        <v>1188</v>
+        <v>340</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013079</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174098</t>
+          <t xml:space="preserve">9844795</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>1350</v>
+        <v>348</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016637</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">5766142</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>660</v>
+        <v>1545</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018924</t>
+          <t xml:space="preserve">100118059</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-20</t>
+          <t xml:space="preserve">2019-04-23</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763717</t>
+          <t xml:space="preserve">5174098</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>815</v>
+        <v>1350</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033117</t>
+          <t xml:space="preserve">200016637</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2019-06-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F57">
-        <v>596</v>
+        <v>660</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">200018924</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2019-08-20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">5763717</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F58">
-        <v>572</v>
+        <v>815</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">200033117</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2936,11 +2936,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
-        <v>448</v>
+        <v>572</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3036,11 +3036,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F61">
-        <v>624</v>
+        <v>552</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5190897</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F62">
-        <v>395</v>
+        <v>448</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034532</t>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-26</t>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5191056</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F63">
-        <v>267</v>
+        <v>624</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034531</t>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-26</t>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9583353</t>
+          <t xml:space="preserve">5190897</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>585</v>
+        <v>395</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">100204046</t>
+          <t xml:space="preserve">200034532</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-31</t>
+          <t xml:space="preserve">2020-07-26</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9744778</t>
+          <t xml:space="preserve">5191056</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059270</t>
+          <t xml:space="preserve">200034531</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-02</t>
+          <t xml:space="preserve">2020-07-26</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763717</t>
+          <t xml:space="preserve">9583353</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F66">
-        <v>498</v>
+        <v>585</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">310019966</t>
+          <t xml:space="preserve">100204046</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-01-10</t>
+          <t xml:space="preserve">2021-01-31</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5190332</t>
+          <t xml:space="preserve">9744778</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>876</v>
+        <v>284</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311014317</t>
+          <t xml:space="preserve">200059270</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-27</t>
+          <t xml:space="preserve">2022-05-02</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193446</t>
+          <t xml:space="preserve">5763717</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F68">
-        <v>1441</v>
+        <v>498</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033835</t>
+          <t xml:space="preserve">310019966</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-15</t>
+          <t xml:space="preserve">2023-01-10</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193446</t>
+          <t xml:space="preserve">5190332</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>665</v>
+        <v>876</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033835</t>
+          <t xml:space="preserve">311014317</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-15</t>
+          <t xml:space="preserve">2023-08-27</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5761773</t>
+          <t xml:space="preserve">5193446</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>8685</v>
+        <v>1441</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311035917</t>
+          <t xml:space="preserve">311033835</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-29</t>
+          <t xml:space="preserve">2024-01-15</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763717</t>
+          <t xml:space="preserve">5193446</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F71">
-        <v>1031</v>
+        <v>665</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156716</t>
+          <t xml:space="preserve">311033835</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-02</t>
+          <t xml:space="preserve">2024-01-15</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766285</t>
+          <t xml:space="preserve">5761773</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,26 +3590,26 @@
         </is>
       </c>
       <c r="F72">
-        <v>1334</v>
+        <v>8685</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216909</t>
+          <t xml:space="preserve">311035917</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2024-01-29</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766433</t>
+          <t xml:space="preserve">5763717</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F73">
-        <v>359</v>
+        <v>1031</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216907</t>
+          <t xml:space="preserve">311156716</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-02-02</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3681,20 +3681,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766433</t>
+          <t xml:space="preserve">5766285</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>529</v>
+        <v>1334</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216907</t>
+          <t xml:space="preserve">311216909</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3736,11 +3736,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F75">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,20 +3781,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7863226</t>
+          <t xml:space="preserve">5766433</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F76">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216899</t>
+          <t xml:space="preserve">311216907</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">100077557</t>
+          <t xml:space="preserve">5766433</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F77">
-        <v>1697</v>
+        <v>390</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218169</t>
+          <t xml:space="preserve">311216907</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5180177</t>
+          <t xml:space="preserve">7863226</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>1883</v>
+        <v>505</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219362</t>
+          <t xml:space="preserve">311216899</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5184436</t>
+          <t xml:space="preserve">100077557</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>394</v>
+        <v>1697</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219292</t>
+          <t xml:space="preserve">311218169</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">306720, 306722, 306721, 306723</t>
+          <t xml:space="preserve">5180177</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>6786</v>
+        <v>1883</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222158</t>
+          <t xml:space="preserve">311219362</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-12</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5177087</t>
+          <t xml:space="preserve">5184436</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>3538</v>
+        <v>394</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222170</t>
+          <t xml:space="preserve">311219292</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-12</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,20 +4081,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">5168237</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F82">
-        <v>271</v>
+        <v>2048</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222176</t>
+          <t xml:space="preserve">311222275</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118230</t>
+          <t xml:space="preserve">5177087</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="F83">
-        <v>5888</v>
+        <v>3538</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222171</t>
+          <t xml:space="preserve">311222170</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806753</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="F84">
-        <v>1166</v>
+        <v>271</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222531</t>
+          <t xml:space="preserve">311222176</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762441</t>
+          <t xml:space="preserve">9118230</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>9997</v>
+        <v>5888</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222424</t>
+          <t xml:space="preserve">311222171</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5192234</t>
+          <t xml:space="preserve">1806753</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>1383</v>
+        <v>1166</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223728</t>
+          <t xml:space="preserve">311222531</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-20</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">5762441</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>601</v>
+        <v>9997</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311222424</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">5763874</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F88">
-        <v>608</v>
+        <v>1495</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311222537</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">5192234</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>596</v>
+        <v>1383</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311223728</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F91">
-        <v>543</v>
+        <v>608</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4586,15 +4586,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>348</v>
+        <v>596</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223881</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181796</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F93">
-        <v>356</v>
+        <v>543</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235291</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5211505</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F94">
-        <v>3500</v>
+        <v>543</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235390</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5211505</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F95">
-        <v>391</v>
+        <v>348</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235392</t>
+          <t xml:space="preserve">311223876</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">308624, 308625</t>
+          <t xml:space="preserve">5181796</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>2356</v>
+        <v>356</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239964</t>
+          <t xml:space="preserve">311235291</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">308625</t>
+          <t xml:space="preserve">5211505</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>2006</v>
+        <v>3500</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239964</t>
+          <t xml:space="preserve">311235390</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">308625</t>
+          <t xml:space="preserve">5211505</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239965</t>
+          <t xml:space="preserve">311235392</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246904</t>
+          <t xml:space="preserve">311246886</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5761357</t>
+          <t xml:space="preserve">7358819</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6740,16 +6740,16 @@
         </is>
       </c>
       <c r="F135">
-        <v>486</v>
+        <v>1188</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257671</t>
+          <t xml:space="preserve">311256730</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6786,15 +6786,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136">
-        <v>1076</v>
+        <v>486</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257671</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6836,11 +6836,11 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F137">
-        <v>2104</v>
+        <v>1076</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6886,11 +6886,11 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F138">
-        <v>1158</v>
+        <v>2104</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589217</t>
+          <t xml:space="preserve">5761357</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F139">
-        <v>288</v>
+        <v>1158</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260488</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-12</t>
+          <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6986,11 +6986,11 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F140">
-        <v>369</v>
+        <v>288</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7036,15 +7036,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F141">
-        <v>446</v>
+        <v>369</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260489</t>
+          <t xml:space="preserve">311260488</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7130115</t>
+          <t xml:space="preserve">8589217</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F142">
-        <v>5802</v>
+        <v>446</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279444</t>
+          <t xml:space="preserve">311260489</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-19</t>
+          <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766417</t>
+          <t xml:space="preserve">7130115</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F143">
-        <v>3020</v>
+        <v>5802</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284651</t>
+          <t xml:space="preserve">311279444</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-20</t>
+          <t xml:space="preserve">2027-10-19</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5180955</t>
+          <t xml:space="preserve">5766417</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F145">
-        <v>1305</v>
+        <v>3020</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315302</t>
+          <t xml:space="preserve">311286413</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-22</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5175321</t>
+          <t xml:space="preserve">5180955</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F146">
-        <v>379</v>
+        <v>1305</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311446554</t>
+          <t xml:space="preserve">311315302</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-29</t>
+          <t xml:space="preserve">2028-05-22</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174369</t>
+          <t xml:space="preserve">5175321</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>288</v>
+        <v>379</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311478741</t>
+          <t xml:space="preserve">311446554</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-26</t>
+          <t xml:space="preserve">2030-06-29</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118161</t>
+          <t xml:space="preserve">5174369</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="F148">
-        <v>495</v>
+        <v>288</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479631</t>
+          <t xml:space="preserve">311478741</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-01</t>
+          <t xml:space="preserve">2030-11-26</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174899</t>
+          <t xml:space="preserve">9118161</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F149">
-        <v>254</v>
+        <v>495</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479972</t>
+          <t xml:space="preserve">311479631</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-02</t>
+          <t xml:space="preserve">2030-12-01</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194278</t>
+          <t xml:space="preserve">5174899</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F150">
-        <v>569</v>
+        <v>254</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480972</t>
+          <t xml:space="preserve">311479972</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-02</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806768</t>
+          <t xml:space="preserve">5194278</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,16 +7540,16 @@
         </is>
       </c>
       <c r="F151">
-        <v>389</v>
+        <v>569</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481278</t>
+          <t xml:space="preserve">311480972</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5765780</t>
+          <t xml:space="preserve">1806768</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F152">
-        <v>485</v>
+        <v>389</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482124</t>
+          <t xml:space="preserve">311481278</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5184581</t>
+          <t xml:space="preserve">5765780</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F153">
-        <v>349</v>
+        <v>485</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483187</t>
+          <t xml:space="preserve">311482124</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-12-11</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F154">
-        <v>262</v>
+        <v>349</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188837</t>
+          <t xml:space="preserve">5184581</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F155">
-        <v>511</v>
+        <v>262</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483525</t>
+          <t xml:space="preserve">311483187</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5192772</t>
+          <t xml:space="preserve">5188837</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="F156">
-        <v>283</v>
+        <v>511</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484901</t>
+          <t xml:space="preserve">311483525</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764713</t>
+          <t xml:space="preserve">5192772</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="F157">
-        <v>7319</v>
+        <v>283</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311489685</t>
+          <t xml:space="preserve">311484901</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-22</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189069</t>
+          <t xml:space="preserve">5764713</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="F158">
-        <v>8202</v>
+        <v>7319</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500456</t>
+          <t xml:space="preserve">311489685</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-04</t>
+          <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7936,15 +7936,15 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F159">
-        <v>300</v>
+        <v>8202</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500458</t>
+          <t xml:space="preserve">311500456</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7981,20 +7981,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">9265859</t>
+          <t xml:space="preserve">5189069</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F160">
-        <v>631</v>
+        <v>300</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500526</t>
+          <t xml:space="preserve">311500458</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5192381</t>
+          <t xml:space="preserve">9265859</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>538</v>
+        <v>631</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514784</t>
+          <t xml:space="preserve">311500526</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-03-04</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9428594</t>
+          <t xml:space="preserve">5192381</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="F162">
-        <v>886</v>
+        <v>538</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311515516</t>
+          <t xml:space="preserve">311514784</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-26</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5177022</t>
+          <t xml:space="preserve">9428594</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="F163">
-        <v>584</v>
+        <v>886</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516132</t>
+          <t xml:space="preserve">311515516</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-28</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8186,11 +8186,11 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F164">
-        <v>354</v>
+        <v>584</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171823</t>
+          <t xml:space="preserve">5177022</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516572</t>
+          <t xml:space="preserve">311516132</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-29</t>
+          <t xml:space="preserve">2031-04-28</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8286,11 +8286,11 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F166">
-        <v>575</v>
+        <v>309</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -8331,20 +8331,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193869</t>
+          <t xml:space="preserve">5171823</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F167">
-        <v>9914</v>
+        <v>575</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516603</t>
+          <t xml:space="preserve">311516572</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8381,20 +8381,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193869, 100770346</t>
+          <t xml:space="preserve">5193869</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F168">
-        <v>983</v>
+        <v>9914</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516590</t>
+          <t xml:space="preserve">311516603</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8431,20 +8431,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186622</t>
+          <t xml:space="preserve">5193869, 100770346</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F169">
-        <v>1388</v>
+        <v>983</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516712</t>
+          <t xml:space="preserve">311516590</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8486,11 +8486,11 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F170">
-        <v>576</v>
+        <v>1388</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -8536,11 +8536,11 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F171">
-        <v>407</v>
+        <v>576</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -8586,11 +8586,11 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>2388</v>
+        <v>407</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -8636,11 +8636,11 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F173">
-        <v>882</v>
+        <v>2388</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -8686,11 +8686,11 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F174">
-        <v>865</v>
+        <v>882</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -8736,15 +8736,15 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F175">
-        <v>328</v>
+        <v>865</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516684</t>
+          <t xml:space="preserve">311516712</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8781,20 +8781,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8029930</t>
+          <t xml:space="preserve">7186622</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F176">
-        <v>1471</v>
+        <v>328</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516734</t>
+          <t xml:space="preserve">311516684</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8836,11 +8836,11 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F177">
-        <v>1067</v>
+        <v>1471</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -8886,11 +8886,11 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F178">
-        <v>1504</v>
+        <v>1067</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8936,11 +8936,11 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F179">
-        <v>2159</v>
+        <v>1504</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5187373</t>
+          <t xml:space="preserve">8029930</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F180">
-        <v>272</v>
+        <v>2159</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646458</t>
+          <t xml:space="preserve">311516734</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035367</t>
+          <t xml:space="preserve">5187373</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9040,16 +9040,16 @@
         </is>
       </c>
       <c r="F181">
-        <v>844</v>
+        <v>272</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655998</t>
+          <t xml:space="preserve">311646458</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-25</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193438</t>
+          <t xml:space="preserve">100035367</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9090,11 +9090,11 @@
         </is>
       </c>
       <c r="F182">
-        <v>4235</v>
+        <v>844</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656138</t>
+          <t xml:space="preserve">311655998</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9136,15 +9136,15 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F183">
-        <v>581</v>
+        <v>4235</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656142</t>
+          <t xml:space="preserve">311656138</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9186,15 +9186,15 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>2630</v>
+        <v>581</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656140</t>
+          <t xml:space="preserve">311656142</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5187374</t>
+          <t xml:space="preserve">5193438</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F185">
-        <v>1841</v>
+        <v>2630</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311658779</t>
+          <t xml:space="preserve">311656140</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-08</t>
+          <t xml:space="preserve">2033-01-25</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9286,11 +9286,11 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F186">
-        <v>668</v>
+        <v>1841</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008282</t>
+          <t xml:space="preserve">5187374</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F187">
-        <v>4535</v>
+        <v>668</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660456</t>
+          <t xml:space="preserve">311658779</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-02-08</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5191980</t>
+          <t xml:space="preserve">100008282</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9390,16 +9390,16 @@
         </is>
       </c>
       <c r="F188">
-        <v>1316</v>
+        <v>4535</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713847</t>
+          <t xml:space="preserve">311660456</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285462</t>
+          <t xml:space="preserve">5191980</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9440,11 +9440,11 @@
         </is>
       </c>
       <c r="F189">
-        <v>311</v>
+        <v>1316</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661671</t>
+          <t xml:space="preserve">311713847</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9486,15 +9486,15 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F190">
-        <v>1068</v>
+        <v>311</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661667</t>
+          <t xml:space="preserve">311661669</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9536,15 +9536,15 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F191">
-        <v>630</v>
+        <v>1068</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661671</t>
+          <t xml:space="preserve">311661667</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5183526</t>
+          <t xml:space="preserve">8285462</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F192">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311681008</t>
+          <t xml:space="preserve">311661669</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-16</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5190498</t>
+          <t xml:space="preserve">5183526</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F193">
-        <v>836</v>
+        <v>627</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713844</t>
+          <t xml:space="preserve">311681008</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-16</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9686,11 +9686,11 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F194">
-        <v>1680</v>
+        <v>836</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -9736,11 +9736,11 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F195">
-        <v>2257</v>
+        <v>1680</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -9786,11 +9786,11 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F196">
-        <v>3154</v>
+        <v>2257</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5183526</t>
+          <t xml:space="preserve">5190498</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F197">
-        <v>355</v>
+        <v>3154</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311681007</t>
+          <t xml:space="preserve">311713844</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-16</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9886,11 +9886,11 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F198">
-        <v>775</v>
+        <v>355</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -9936,11 +9936,11 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F199">
-        <v>3520</v>
+        <v>775</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">306221, 306222, 306223, 306224, 306225, 306229, 306226, 306227, 306228</t>
+          <t xml:space="preserve">5183526</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F200">
-        <v>8548</v>
+        <v>3520</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311776578</t>
+          <t xml:space="preserve">311681007</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-06</t>
+          <t xml:space="preserve">2033-05-16</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">

--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lodsvej 9</t>
+          <t xml:space="preserve">Billundvej 1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100374038</t>
+          <t xml:space="preserve">734787, 5194083</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>1318</v>
+        <v>576</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgårdsvej 5</t>
+          <t xml:space="preserve">Bygaden 18C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496986</t>
+          <t xml:space="preserve">734985, 100055830</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>822</v>
+        <v>653</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgårdsvej 1</t>
+          <t xml:space="preserve">Christen Kolds Vej 14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496986</t>
+          <t xml:space="preserve">5171828</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H4">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispegade 15</t>
+          <t xml:space="preserve">Christian X's Vej 41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,7 +281,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">306221, 306222, 306223, 306224, 306225, 306229, 306226, 306227, 306228</t>
+          <t xml:space="preserve">5761917</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="H5">
-        <v>8548</v>
+        <v>1477</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simmerstedvej 1A</t>
+          <t xml:space="preserve">Christiansfeldvej 12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">306720, 306722, 306721, 306723</t>
+          <t xml:space="preserve">5760988</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H6">
-        <v>6786</v>
+        <v>273</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkealle 22A</t>
+          <t xml:space="preserve">Christiansfeldvej 35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">308624, 308625</t>
+          <t xml:space="preserve">734667, 5764599</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>2356</v>
+        <v>1775</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkealle 22A</t>
+          <t xml:space="preserve">Christiansfeldvej 39A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">308625</t>
+          <t xml:space="preserve">5764519</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>2006</v>
+        <v>2651</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkealle 22A</t>
+          <t xml:space="preserve">Damstien 28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">308625</t>
+          <t xml:space="preserve">734453, 5764861</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H9">
-        <v>421</v>
+        <v>600</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 14</t>
+          <t xml:space="preserve">Fjordagervej 44</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171828</t>
+          <t xml:space="preserve">734690, 5177090</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>532</v>
+        <v>571</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9E</t>
+          <t xml:space="preserve">Gammel Bevtoftvej 17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181377</t>
+          <t xml:space="preserve">5188474</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H11">
-        <v>806</v>
+        <v>584</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9E</t>
+          <t xml:space="preserve">Harken 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181676</t>
+          <t xml:space="preserve">735009, 5186659</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>814</v>
+        <v>1161</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9E</t>
+          <t xml:space="preserve">Højmarken 51</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181676</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H13">
-        <v>1474</v>
+        <v>560</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9E</t>
+          <t xml:space="preserve">Højmarken 51</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181676</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H14">
-        <v>3164</v>
+        <v>560</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Lindetvej 5</t>
+          <t xml:space="preserve">Højmarken 51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6560</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188218</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H15">
-        <v>497</v>
+        <v>1283</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Lindetvej 5</t>
+          <t xml:space="preserve">Jomfrustien 34</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6560</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188218</t>
+          <t xml:space="preserve">735045, 1809456</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>372</v>
+        <v>1573</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Bevtoftvej 17</t>
+          <t xml:space="preserve">Klosteret 33</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188474</t>
+          <t xml:space="preserve">734570, 5763051</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>584</v>
+        <v>425</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unionvej 3</t>
+          <t xml:space="preserve">Kløvermarken 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189044</t>
+          <t xml:space="preserve">734677, 5764684</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H18">
-        <v>663</v>
+        <v>336</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unionvej 4C</t>
+          <t xml:space="preserve">Kløvervænget 1B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189069</t>
+          <t xml:space="preserve">9583353</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H19">
-        <v>1656</v>
+        <v>585</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglykke 9</t>
+          <t xml:space="preserve">Kløvervænget 1C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189188</t>
+          <t xml:space="preserve">9583353</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H20">
-        <v>425</v>
+        <v>621</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekanten 17</t>
+          <t xml:space="preserve">Lilholtvej 10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193446</t>
+          <t xml:space="preserve">9744778</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H21">
-        <v>630</v>
+        <v>340</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 80</t>
+          <t xml:space="preserve">Lodsvej 9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5760218</t>
+          <t xml:space="preserve">100374038</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H22">
-        <v>392</v>
+        <v>1318</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansfeldvej 12</t>
+          <t xml:space="preserve">Møllesvinget 23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5760988</t>
+          <t xml:space="preserve">8589217</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>273</v>
+        <v>869</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Vej 41</t>
+          <t xml:space="preserve">Odinsvej 3B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5761917</t>
+          <t xml:space="preserve">734655, 5765780</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H24">
-        <v>1477</v>
+        <v>417</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,26 +1471,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 9</t>
+          <t xml:space="preserve">Overgårdsvej 1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762441</t>
+          <t xml:space="preserve">1496986</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H25">
-        <v>1733</v>
+        <v>498</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,26 +1531,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Havnen 17</t>
+          <t xml:space="preserve">Overgårdsvej 1B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762992</t>
+          <t xml:space="preserve">9254128</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>611</v>
+        <v>274</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Havnen 15A</t>
+          <t xml:space="preserve">Overgårdsvej 5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763342</t>
+          <t xml:space="preserve">1496986</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>291</v>
+        <v>822</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansfeldvej 39A</t>
+          <t xml:space="preserve">Slagtergade 66</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764519</t>
+          <t xml:space="preserve">7130187</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="H29">
-        <v>2651</v>
+        <v>283</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 3</t>
+          <t xml:space="preserve">Slotsvej 6B</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766303</t>
+          <t xml:space="preserve">734426, 5182334</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H30">
-        <v>1248</v>
+        <v>388</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydhavnsvej 1F</t>
+          <t xml:space="preserve">Solsikkevej 3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766667</t>
+          <t xml:space="preserve">5766303</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>274</v>
+        <v>1248</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slagtergade 66</t>
+          <t xml:space="preserve">Stadionvej 1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7130187</t>
+          <t xml:space="preserve">9118463</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="H32">
-        <v>283</v>
+        <v>594</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsvej 6B</t>
+          <t xml:space="preserve">Stadionvej 9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">734426, 5182334</t>
+          <t xml:space="preserve">5762441</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H33">
-        <v>388</v>
+        <v>1733</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damstien 28</t>
+          <t xml:space="preserve">Stadionvej 9E</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">734453, 5764861</t>
+          <t xml:space="preserve">5181377</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H34">
-        <v>600</v>
+        <v>806</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klosteret 33</t>
+          <t xml:space="preserve">Stadionvej 9E</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">734570, 5763051</t>
+          <t xml:space="preserve">5181676</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H35">
-        <v>425</v>
+        <v>814</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 3B</t>
+          <t xml:space="preserve">Stadionvej 9E</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">734655, 5765780</t>
+          <t xml:space="preserve">5181676</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H36">
-        <v>417</v>
+        <v>1474</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansfeldvej 35</t>
+          <t xml:space="preserve">Stadionvej 9E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">734667, 5764599</t>
+          <t xml:space="preserve">5181676</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H37">
-        <v>1775</v>
+        <v>3164</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 1</t>
+          <t xml:space="preserve">Storegade 80</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">734677, 5764684</t>
+          <t xml:space="preserve">5760218</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordagervej 44</t>
+          <t xml:space="preserve">Sydhavnsvej 1F</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">734690, 5177090</t>
+          <t xml:space="preserve">5766667</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H39">
-        <v>571</v>
+        <v>274</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Billundvej 1</t>
+          <t xml:space="preserve">Sønderbyvej 28</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">734787, 5194083</t>
+          <t xml:space="preserve">9844795</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H40">
-        <v>576</v>
+        <v>348</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 18C</t>
+          <t xml:space="preserve">Tinglykke 9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">734985, 100055830</t>
+          <t xml:space="preserve">5189188</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>653</v>
+        <v>425</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harken 1</t>
+          <t xml:space="preserve">Trekanten 17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">735009, 5186659</t>
+          <t xml:space="preserve">5193446</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H42">
-        <v>1161</v>
+        <v>630</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,17 +2551,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jomfrustien 34</t>
+          <t xml:space="preserve">Tårnvej 6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">735045, 1809456</t>
+          <t xml:space="preserve">8473404</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="H43">
-        <v>1573</v>
+        <v>358</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,17 +2611,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 6</t>
+          <t xml:space="preserve">Unionvej 3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8473404</t>
+          <t xml:space="preserve">5189044</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="H44">
-        <v>358</v>
+        <v>663</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllesvinget 23</t>
+          <t xml:space="preserve">Unionvej 4C</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589217</t>
+          <t xml:space="preserve">5189069</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H45">
-        <v>869</v>
+        <v>1656</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarken 51</t>
+          <t xml:space="preserve">Ved Havnen 15A</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">5763342</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H46">
-        <v>560</v>
+        <v>291</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,26 +2791,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarken 51</t>
+          <t xml:space="preserve">Ved Havnen 17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">5762992</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H47">
-        <v>560</v>
+        <v>611</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,26 +2851,26 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarken 51</t>
+          <t xml:space="preserve">Øster Lindetvej 5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6560</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">5188218</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>1283</v>
+        <v>497</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,26 +2911,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 1</t>
+          <t xml:space="preserve">Øster Lindetvej 5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6560</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118463</t>
+          <t xml:space="preserve">5188218</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H49">
-        <v>594</v>
+        <v>372</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgårdsvej 1B</t>
+          <t xml:space="preserve">Kløvervej 87B</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254128</t>
+          <t xml:space="preserve">5766142</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,21 +2990,21 @@
         </is>
       </c>
       <c r="H50">
-        <v>274</v>
+        <v>1545</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100118059</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-04-23</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervænget 1B</t>
+          <t xml:space="preserve">Skovbyvej 2C</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9583353</t>
+          <t xml:space="preserve">5174098</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>585</v>
+        <v>1350</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016637</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-30</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3091,40 +3091,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervænget 1C</t>
+          <t xml:space="preserve">Højmarken 51</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9583353</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H52">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200018924</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3151,40 +3151,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lilholtvej 10</t>
+          <t xml:space="preserve">A.D. Jørgensens Vej 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9744778</t>
+          <t xml:space="preserve">5763717</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H53">
-        <v>340</v>
+        <v>815</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033117</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3211,40 +3211,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderbyvej 28</t>
+          <t xml:space="preserve">Vilstrupvej 120</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844795</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>348</v>
+        <v>596</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervej 87B</t>
+          <t xml:space="preserve">Vilstrupvej 120A</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766142</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H55">
-        <v>1545</v>
+        <v>572</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100118059</t>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-23</t>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbyvej 2C</t>
+          <t xml:space="preserve">Vilstrupvej 120B</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,25 +3341,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174098</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H56">
-        <v>1350</v>
+        <v>552</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016637</t>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-30</t>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,35 +3391,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarken 51</t>
+          <t xml:space="preserve">Vilstrupvej 120C</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H57">
-        <v>660</v>
+        <v>448</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018924</t>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-20</t>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.D. Jørgensens Vej 1</t>
+          <t xml:space="preserve">Vilstrupvej 120D</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763717</t>
+          <t xml:space="preserve">5764717</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H58">
-        <v>815</v>
+        <v>624</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033117</t>
+          <t xml:space="preserve">200033379</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vilstrupvej 120</t>
+          <t xml:space="preserve">Hovedgaden Øst 61A</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">5190897</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>596</v>
+        <v>395</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">200034532</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2020-07-26</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vilstrupvej 120A</t>
+          <t xml:space="preserve">Stationsvej 6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">5191056</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>572</v>
+        <v>267</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">200034531</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2020-07-26</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vilstrupvej 120B</t>
+          <t xml:space="preserve">Kløvervænget 1A</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">9583353</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,16 +3650,16 @@
         </is>
       </c>
       <c r="H61">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">100204046</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2021-01-31</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vilstrupvej 120C</t>
+          <t xml:space="preserve">Lilholtvej 10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">9744778</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>448</v>
+        <v>284</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">200059270</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2022-05-02</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vilstrupvej 120D</t>
+          <t xml:space="preserve">Louisevej 8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764717</t>
+          <t xml:space="preserve">5763717</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H63">
-        <v>624</v>
+        <v>498</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033379</t>
+          <t xml:space="preserve">310019966</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-01</t>
+          <t xml:space="preserve">2023-01-10</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden Øst 61A</t>
+          <t xml:space="preserve">Marie Skaus Vej 5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6560</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5190897</t>
+          <t xml:space="preserve">5190332</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3830,16 +3830,16 @@
         </is>
       </c>
       <c r="H64">
-        <v>395</v>
+        <v>876</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034532</t>
+          <t xml:space="preserve">311014317</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-26</t>
+          <t xml:space="preserve">2023-08-27</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 6</t>
+          <t xml:space="preserve">Trekanten 15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5191056</t>
+          <t xml:space="preserve">5193446</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>267</v>
+        <v>665</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034531</t>
+          <t xml:space="preserve">311033835</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-26</t>
+          <t xml:space="preserve">2024-01-15</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,35 +3931,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervænget 1A</t>
+          <t xml:space="preserve">Trekanten 17</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">9583353</t>
+          <t xml:space="preserve">5193446</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H66">
-        <v>585</v>
+        <v>1441</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">100204046</t>
+          <t xml:space="preserve">311033835</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-31</t>
+          <t xml:space="preserve">2024-01-15</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lilholtvej 10</t>
+          <t xml:space="preserve">Christian X's Vej 39</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">9744778</t>
+          <t xml:space="preserve">5761773</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>284</v>
+        <v>8685</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059270</t>
+          <t xml:space="preserve">311035917</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-05-02</t>
+          <t xml:space="preserve">2024-01-29</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4066,20 +4066,20 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H68">
-        <v>498</v>
+        <v>1031</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">310019966</t>
+          <t xml:space="preserve">311156716</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-01-10</t>
+          <t xml:space="preserve">2026-02-02</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marie Skaus Vej 5</t>
+          <t xml:space="preserve">Solsikkevej 2A</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6560</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5190332</t>
+          <t xml:space="preserve">5766285</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,26 +4130,26 @@
         </is>
       </c>
       <c r="H69">
-        <v>876</v>
+        <v>1334</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311014317</t>
+          <t xml:space="preserve">311216909</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-27</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4171,45 +4171,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekanten 17</t>
+          <t xml:space="preserve">Solsikkevej 4A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193446</t>
+          <t xml:space="preserve">5766433</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70">
-        <v>1441</v>
+        <v>359</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033835</t>
+          <t xml:space="preserve">311216907</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-15</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4231,45 +4231,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekanten 15</t>
+          <t xml:space="preserve">Solsikkevej 4B</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193446</t>
+          <t xml:space="preserve">5766433</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H71">
-        <v>665</v>
+        <v>529</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311033835</t>
+          <t xml:space="preserve">311216907</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-15</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Vej 39</t>
+          <t xml:space="preserve">Solsikkevej 4C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,35 +4301,35 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5761773</t>
+          <t xml:space="preserve">5766433</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H72">
-        <v>8685</v>
+        <v>390</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311035917</t>
+          <t xml:space="preserve">311216907</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-29</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Louisevej 8</t>
+          <t xml:space="preserve">Thrigesvej 1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,35 +4361,35 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763717</t>
+          <t xml:space="preserve">7863226</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>1031</v>
+        <v>505</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311156716</t>
+          <t xml:space="preserve">311216899</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-02</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 2A</t>
+          <t xml:space="preserve">Ved Havnen 20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766285</t>
+          <t xml:space="preserve">100077557</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>1334</v>
+        <v>1697</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216909</t>
+          <t xml:space="preserve">311218169</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 4A</t>
+          <t xml:space="preserve">Bygaden 21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766433</t>
+          <t xml:space="preserve">5184436</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216907</t>
+          <t xml:space="preserve">311219292</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 4B</t>
+          <t xml:space="preserve">Øsby Stadionvej 6</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,25 +4541,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766433</t>
+          <t xml:space="preserve">5180177</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>529</v>
+        <v>1883</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216907</t>
+          <t xml:space="preserve">311219362</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 4C</t>
+          <t xml:space="preserve">Højmarken 51</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766433</t>
+          <t xml:space="preserve">8940516</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>390</v>
+        <v>271</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216907</t>
+          <t xml:space="preserve">311222176</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrigesvej 1</t>
+          <t xml:space="preserve">Simmerstedvej 1A</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7863226</t>
+          <t xml:space="preserve">306720, 306722, 306721, 306723</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>505</v>
+        <v>6786</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216899</t>
+          <t xml:space="preserve">311222158</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Havnen 20</t>
+          <t xml:space="preserve">Skolebakken 10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,25 +4721,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">100077557</t>
+          <t xml:space="preserve">5168237</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H79">
-        <v>1697</v>
+        <v>2048</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218169</t>
+          <t xml:space="preserve">311222275</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øsby Stadionvej 6</t>
+          <t xml:space="preserve">Starup Skolevej 33A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5180177</t>
+          <t xml:space="preserve">5177087</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="H80">
-        <v>1883</v>
+        <v>3538</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219362</t>
+          <t xml:space="preserve">311222170</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 21</t>
+          <t xml:space="preserve">Starup Skolevej 35A</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5184436</t>
+          <t xml:space="preserve">9118230</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="H81">
-        <v>394</v>
+        <v>5888</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219292</t>
+          <t xml:space="preserve">311222171</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 10</t>
+          <t xml:space="preserve">Stadionvej 5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,25 +4901,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5168237</t>
+          <t xml:space="preserve">5762441</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>2048</v>
+        <v>9997</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222275</t>
+          <t xml:space="preserve">311222424</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-12</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starup Skolevej 33A</t>
+          <t xml:space="preserve">Thrigesvej 51</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,25 +4961,25 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5177087</t>
+          <t xml:space="preserve">5763874</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H83">
-        <v>3538</v>
+        <v>1495</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222170</t>
+          <t xml:space="preserve">311222537</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-12</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarken 51</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940516</t>
+          <t xml:space="preserve">1806753</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="H84">
-        <v>271</v>
+        <v>1166</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222176</t>
+          <t xml:space="preserve">311222531</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-12</t>
+          <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,35 +5071,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starup Skolevej 35A</t>
+          <t xml:space="preserve">Danmarksgade 8</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118230</t>
+          <t xml:space="preserve">5192234</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H85">
-        <v>5888</v>
+        <v>1383</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222171</t>
+          <t xml:space="preserve">311223728</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-12</t>
+          <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Odinsvej 186A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,25 +5141,25 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806753</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H86">
-        <v>1166</v>
+        <v>348</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222531</t>
+          <t xml:space="preserve">311223881</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 5</t>
+          <t xml:space="preserve">Odinsvej 186B</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762441</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>9997</v>
+        <v>601</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222424</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thrigesvej 51</t>
+          <t xml:space="preserve">Odinsvej 186C</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5763874</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H88">
-        <v>1495</v>
+        <v>596</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222537</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-13</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 8</t>
+          <t xml:space="preserve">Odinsvej 186D</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5192234</t>
+          <t xml:space="preserve">5194351</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H89">
-        <v>1383</v>
+        <v>543</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223728</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-20</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 186B</t>
+          <t xml:space="preserve">Odinsvej 186E</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5386,15 +5386,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H90">
-        <v>601</v>
+        <v>543</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 186C</t>
+          <t xml:space="preserve">Skolekobbel 42</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">5181796</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>596</v>
+        <v>356</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311235291</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 186D</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">5211505</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>543</v>
+        <v>3500</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311235390</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 186E</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">5211505</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H94">
-        <v>543</v>
+        <v>391</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311235392</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,35 +5671,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 186A</t>
+          <t xml:space="preserve">Kirkealle 22A</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194351</t>
+          <t xml:space="preserve">308624, 308625</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H95">
-        <v>348</v>
+        <v>2356</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311239964</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolekobbel 42</t>
+          <t xml:space="preserve">Kirkealle 22A</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,25 +5741,25 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5181796</t>
+          <t xml:space="preserve">308625</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H96">
-        <v>356</v>
+        <v>2006</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235291</t>
+          <t xml:space="preserve">311239964</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kirkealle 22A</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5211505</t>
+          <t xml:space="preserve">308625</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H97">
-        <v>3500</v>
+        <v>421</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235390</t>
+          <t xml:space="preserve">311239965</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Slotsvej 6A</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5211505</t>
+          <t xml:space="preserve">5180891</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>391</v>
+        <v>568</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235392</t>
+          <t xml:space="preserve">311240950</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-04-12</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsvej 6A</t>
+          <t xml:space="preserve">Christiansfeldvej 31D</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5180891</t>
+          <t xml:space="preserve">100035061</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>568</v>
+        <v>1808</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311240950</t>
+          <t xml:space="preserve">311242602</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-12</t>
+          <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansfeldvej 31D</t>
+          <t xml:space="preserve">Godthåbsvej 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035061</t>
+          <t xml:space="preserve">5172307</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>1808</v>
+        <v>504</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242602</t>
+          <t xml:space="preserve">311245301</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-05-04</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 2</t>
+          <t xml:space="preserve">Krügersvej 45</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6541</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5172307</t>
+          <t xml:space="preserve">5203112</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="H101">
-        <v>504</v>
+        <v>1306</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245301</t>
+          <t xml:space="preserve">311246471</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-04</t>
+          <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H102">
-        <v>1306</v>
+        <v>681</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6166,11 +6166,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H103">
-        <v>681</v>
+        <v>301</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krügersvej 45</t>
+          <t xml:space="preserve">Vonsbækvej 88</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6541</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5203112</t>
+          <t xml:space="preserve">5178716</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>301</v>
+        <v>1501</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246471</t>
+          <t xml:space="preserve">311246904</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-10</t>
+          <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vonsbækvej 88</t>
+          <t xml:space="preserve">Buegade 11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5178716</t>
+          <t xml:space="preserve">7095441</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>1501</v>
+        <v>2139</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246886</t>
+          <t xml:space="preserve">311248324</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-11</t>
+          <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H106">
-        <v>2139</v>
+        <v>2620</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buegade 11</t>
+          <t xml:space="preserve">Buegade 11A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6406,11 +6406,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H107">
-        <v>2620</v>
+        <v>419</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buegade 11A</t>
+          <t xml:space="preserve">Buegade 9</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,25 +6461,25 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095441</t>
+          <t xml:space="preserve">5764837</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>419</v>
+        <v>294</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248324</t>
+          <t xml:space="preserve">311248987</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-18</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buegade 9</t>
+          <t xml:space="preserve">Christen Kolds Vej 12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,25 +6521,25 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764837</t>
+          <t xml:space="preserve">5171828</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H109">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248987</t>
+          <t xml:space="preserve">311251645</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 12</t>
+          <t xml:space="preserve">Hoptrup Hovedgade 66</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171828</t>
+          <t xml:space="preserve">5174098</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H110">
-        <v>331</v>
+        <v>1743</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251645</t>
+          <t xml:space="preserve">311253219</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6646,15 +6646,15 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H111">
-        <v>1743</v>
+        <v>503</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253219</t>
+          <t xml:space="preserve">311322936</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoptrup Hovedgade 66</t>
+          <t xml:space="preserve">Ryes Møllevej 15A</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,25 +6701,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174098</t>
+          <t xml:space="preserve">5764728</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>503</v>
+        <v>759</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311322936</t>
+          <t xml:space="preserve">311253626</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-06-13</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryes Møllevej 15A</t>
+          <t xml:space="preserve">Christen Kolds Vej 10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,25 +6761,25 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764728</t>
+          <t xml:space="preserve">5171828</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H113">
-        <v>759</v>
+        <v>1368</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253626</t>
+          <t xml:space="preserve">311254124</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-13</t>
+          <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 10C</t>
+          <t xml:space="preserve">Christen Kolds Vej 10A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6886,11 +6886,11 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H115">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6946,11 +6946,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>888</v>
+        <v>1015</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 10A</t>
+          <t xml:space="preserve">Christen Kolds Vej 10B</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H117">
@@ -7066,11 +7066,11 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H118">
-        <v>1015</v>
+        <v>1146</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 10B</t>
+          <t xml:space="preserve">Christen Kolds Vej 10C</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7126,11 +7126,11 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H119">
-        <v>1146</v>
+        <v>876</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 10D</t>
+          <t xml:space="preserve">Christen Kolds Vej 10C</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7186,11 +7186,11 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H120">
-        <v>1965</v>
+        <v>1046</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 10</t>
+          <t xml:space="preserve">Christen Kolds Vej 10D</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7246,11 +7246,11 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H121">
-        <v>1368</v>
+        <v>1965</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 10C</t>
+          <t xml:space="preserve">Avnøvej 7</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,25 +7421,25 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171828</t>
+          <t xml:space="preserve">5168258</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H124">
-        <v>1046</v>
+        <v>1051</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254124</t>
+          <t xml:space="preserve">311254531</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-15</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avnøvej 7</t>
+          <t xml:space="preserve">Christen Kolds Vej 4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5168258</t>
+          <t xml:space="preserve">5764509</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="H125">
-        <v>1051</v>
+        <v>535</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254531</t>
+          <t xml:space="preserve">311254487</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7546,11 +7546,11 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H126">
-        <v>535</v>
+        <v>280</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christen Kolds Vej 4</t>
+          <t xml:space="preserve">Kærsmindevej 3A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,25 +7601,25 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764509</t>
+          <t xml:space="preserve">5174928</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H127">
-        <v>280</v>
+        <v>1636</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254487</t>
+          <t xml:space="preserve">311254832</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærsmindevej 3A</t>
+          <t xml:space="preserve">Flovtvej 1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174928</t>
+          <t xml:space="preserve">5180056</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>1636</v>
+        <v>734</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254832</t>
+          <t xml:space="preserve">311255374</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flovtvej 1</t>
+          <t xml:space="preserve">Øsby Nedergade 30</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H129">
-        <v>734</v>
+        <v>2946</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øsby Nedergade 30</t>
+          <t xml:space="preserve">Marstrup Bygade 115A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5180056</t>
+          <t xml:space="preserve">9118180</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>2946</v>
+        <v>799</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255374</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marstrup Bygade 115A</t>
+          <t xml:space="preserve">Marstrup Bygade 115B</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7846,15 +7846,15 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H131">
-        <v>799</v>
+        <v>608</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marstrup Bygade 115B</t>
+          <t xml:space="preserve">Møllesvinget 38</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7901,25 +7901,25 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118180</t>
+          <t xml:space="preserve">7835785</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H132">
-        <v>608</v>
+        <v>749</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311256426</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7966,11 +7966,11 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H133">
-        <v>749</v>
+        <v>373</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllesvinget 38</t>
+          <t xml:space="preserve">Lembckesvej 2A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,25 +8021,25 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">7835785</t>
+          <t xml:space="preserve">7358819</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H134">
-        <v>373</v>
+        <v>1188</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256426</t>
+          <t xml:space="preserve">311256730</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lembckesvej 2A</t>
+          <t xml:space="preserve">Christiansfeldvej 14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7358819</t>
+          <t xml:space="preserve">5761357</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H135">
-        <v>1188</v>
+        <v>1158</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256730</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257834</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257834</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansfeldvej 14</t>
+          <t xml:space="preserve">Møllesvinget 23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,25 +8321,25 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5761357</t>
+          <t xml:space="preserve">8589217</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H139">
-        <v>1158</v>
+        <v>288</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257834</t>
+          <t xml:space="preserve">311260488</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8386,11 +8386,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H140">
-        <v>288</v>
+        <v>369</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8446,15 +8446,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H141">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260488</t>
+          <t xml:space="preserve">311260489</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllesvinget 23</t>
+          <t xml:space="preserve">Moltrupvej 3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,25 +8501,25 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589217</t>
+          <t xml:space="preserve">7130115</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H142">
-        <v>446</v>
+        <v>5802</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260489</t>
+          <t xml:space="preserve">311279444</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-12</t>
+          <t xml:space="preserve">2027-10-19</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moltrupvej 3</t>
+          <t xml:space="preserve">Kløvermarken 2</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,25 +8561,25 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7130115</t>
+          <t xml:space="preserve">5766417</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>5802</v>
+        <v>8034</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279444</t>
+          <t xml:space="preserve">311286358</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-19</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 2</t>
+          <t xml:space="preserve">Kløvermarken 2A</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8626,15 +8626,15 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H144">
-        <v>8034</v>
+        <v>3020</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286358</t>
+          <t xml:space="preserve">311286413</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 2A</t>
+          <t xml:space="preserve">Kongevej 1B</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6510</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5766417</t>
+          <t xml:space="preserve">5180955</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H145">
-        <v>3020</v>
+        <v>1305</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286413</t>
+          <t xml:space="preserve">311315302</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2028-05-22</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,17 +8731,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 1B</t>
+          <t xml:space="preserve">Gåsevig 29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6510</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5180955</t>
+          <t xml:space="preserve">5175321</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8750,16 +8750,16 @@
         </is>
       </c>
       <c r="H146">
-        <v>1305</v>
+        <v>379</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315302</t>
+          <t xml:space="preserve">311446554</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-22</t>
+          <t xml:space="preserve">2030-06-29</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gåsevig 29</t>
+          <t xml:space="preserve">Lillegård 7</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5175321</t>
+          <t xml:space="preserve">5174369</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8810,16 +8810,16 @@
         </is>
       </c>
       <c r="H147">
-        <v>379</v>
+        <v>288</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311446554</t>
+          <t xml:space="preserve">311478741</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-29</t>
+          <t xml:space="preserve">2030-11-26</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lillegård 7</t>
+          <t xml:space="preserve">Hoptrup Hovedgade 60</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174369</t>
+          <t xml:space="preserve">9118161</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8870,16 +8870,16 @@
         </is>
       </c>
       <c r="H148">
-        <v>288</v>
+        <v>495</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311478741</t>
+          <t xml:space="preserve">311479631</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-26</t>
+          <t xml:space="preserve">2030-12-01</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoptrup Hovedgade 60</t>
+          <t xml:space="preserve">Kærsmindevej 5</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,25 +8921,25 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118161</t>
+          <t xml:space="preserve">5174899</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H149">
-        <v>495</v>
+        <v>254</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479631</t>
+          <t xml:space="preserve">311479972</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-01</t>
+          <t xml:space="preserve">2030-12-02</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,35 +8971,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærsmindevej 5</t>
+          <t xml:space="preserve">Huginsvang 85</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5174899</t>
+          <t xml:space="preserve">5194278</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H150">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479972</t>
+          <t xml:space="preserve">311480972</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-02</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huginsvang 85</t>
+          <t xml:space="preserve">Glentevej 39</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5194278</t>
+          <t xml:space="preserve">1806768</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="H151">
-        <v>569</v>
+        <v>389</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480972</t>
+          <t xml:space="preserve">311481278</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,35 +9091,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glentevej 39</t>
+          <t xml:space="preserve">Odinsvej 3A</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806768</t>
+          <t xml:space="preserve">5765780</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H152">
-        <v>389</v>
+        <v>485</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481278</t>
+          <t xml:space="preserve">311482124</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2030-12-11</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,35 +9151,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 3A</t>
+          <t xml:space="preserve">Bygaden 18</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5765780</t>
+          <t xml:space="preserve">5184581</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H153">
-        <v>485</v>
+        <v>349</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482124</t>
+          <t xml:space="preserve">311483187</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9226,11 +9226,11 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H154">
-        <v>349</v>
+        <v>262</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 18</t>
+          <t xml:space="preserve">Naffet 21</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5184581</t>
+          <t xml:space="preserve">5188837</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>262</v>
+        <v>511</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483187</t>
+          <t xml:space="preserve">311483525</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-16</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naffet 21</t>
+          <t xml:space="preserve">Præstegårdsvej 20A</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5188837</t>
+          <t xml:space="preserve">5192772</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,16 +9350,16 @@
         </is>
       </c>
       <c r="H156">
-        <v>511</v>
+        <v>283</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483525</t>
+          <t xml:space="preserve">311484901</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,17 +9391,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 20A</t>
+          <t xml:space="preserve">Gammel Hørregårdsvej 29</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5192772</t>
+          <t xml:space="preserve">5764713</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9410,16 +9410,16 @@
         </is>
       </c>
       <c r="H157">
-        <v>283</v>
+        <v>7319</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484901</t>
+          <t xml:space="preserve">311489685</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-23</t>
+          <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Hørregårdsvej 29</t>
+          <t xml:space="preserve">Stadionparken 5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5764713</t>
+          <t xml:space="preserve">9265859</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,16 +9470,16 @@
         </is>
       </c>
       <c r="H158">
-        <v>7319</v>
+        <v>631</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311489685</t>
+          <t xml:space="preserve">311500526</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-22</t>
+          <t xml:space="preserve">2031-03-04</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionparken 5</t>
+          <t xml:space="preserve">Højgade 17</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">9265859</t>
+          <t xml:space="preserve">5192381</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9650,16 +9650,16 @@
         </is>
       </c>
       <c r="H161">
-        <v>631</v>
+        <v>538</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500526</t>
+          <t xml:space="preserve">311514784</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-04</t>
+          <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgade 17</t>
+          <t xml:space="preserve">Danmarksgade 16</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5192381</t>
+          <t xml:space="preserve">9428594</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,16 +9710,16 @@
         </is>
       </c>
       <c r="H162">
-        <v>538</v>
+        <v>886</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311514784</t>
+          <t xml:space="preserve">311515516</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-23</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danmarksgade 16</t>
+          <t xml:space="preserve">Tåsingevej 125</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">9428594</t>
+          <t xml:space="preserve">5177022</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9770,16 +9770,16 @@
         </is>
       </c>
       <c r="H163">
-        <v>886</v>
+        <v>584</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311515516</t>
+          <t xml:space="preserve">311516132</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-26</t>
+          <t xml:space="preserve">2031-04-28</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9826,11 +9826,11 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H164">
-        <v>584</v>
+        <v>354</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -9871,35 +9871,35 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tåsingevej 125</t>
+          <t xml:space="preserve">Jernhytvej 2A</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5177022</t>
+          <t xml:space="preserve">7186622</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H165">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516132</t>
+          <t xml:space="preserve">311516684</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-28</t>
+          <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,30 +9931,30 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ole Rømers Vej 25D</t>
+          <t xml:space="preserve">Jernhytvej 2B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171823</t>
+          <t xml:space="preserve">7186622</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H166">
-        <v>309</v>
+        <v>407</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516572</t>
+          <t xml:space="preserve">311516712</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,30 +9991,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ole Rømers Vej 25F</t>
+          <t xml:space="preserve">Jernhytvej 2B</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171823</t>
+          <t xml:space="preserve">7186622</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H167">
-        <v>575</v>
+        <v>2388</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516572</t>
+          <t xml:space="preserve">311516712</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionparken 7</t>
+          <t xml:space="preserve">Jernhytvej 2C</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,20 +10061,20 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193869</t>
+          <t xml:space="preserve">7186622</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>9914</v>
+        <v>1388</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516603</t>
+          <t xml:space="preserve">311516712</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionparken 7</t>
+          <t xml:space="preserve">Jyllandsgade 29</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,20 +10121,20 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193869, 100770346</t>
+          <t xml:space="preserve">7186622</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H169">
-        <v>983</v>
+        <v>576</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516590</t>
+          <t xml:space="preserve">311516712</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernhytvej 2C</t>
+          <t xml:space="preserve">Jyllandsgade 29</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10186,11 +10186,11 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H170">
-        <v>1388</v>
+        <v>882</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -10246,11 +10246,11 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H171">
-        <v>576</v>
+        <v>865</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -10291,30 +10291,30 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernhytvej 2B</t>
+          <t xml:space="preserve">Kirkevej 10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6560</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186622</t>
+          <t xml:space="preserve">8029930</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H172">
-        <v>407</v>
+        <v>1471</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516712</t>
+          <t xml:space="preserve">311516734</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,17 +10351,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernhytvej 2B</t>
+          <t xml:space="preserve">Kirkevej 10</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6560</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186622</t>
+          <t xml:space="preserve">8029930</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10370,11 +10370,11 @@
         </is>
       </c>
       <c r="H173">
-        <v>2388</v>
+        <v>1067</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516712</t>
+          <t xml:space="preserve">311516734</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jyllandsgade 29</t>
+          <t xml:space="preserve">Kirkevej 10</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6560</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186622</t>
+          <t xml:space="preserve">8029930</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10430,11 +10430,11 @@
         </is>
       </c>
       <c r="H174">
-        <v>882</v>
+        <v>1504</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516712</t>
+          <t xml:space="preserve">311516734</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10471,30 +10471,30 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jyllandsgade 29</t>
+          <t xml:space="preserve">Ole Rømers Vej 25D</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186622</t>
+          <t xml:space="preserve">5171823</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H175">
-        <v>865</v>
+        <v>309</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516712</t>
+          <t xml:space="preserve">311516572</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10531,30 +10531,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernhytvej 2A</t>
+          <t xml:space="preserve">Ole Rømers Vej 25F</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7186622</t>
+          <t xml:space="preserve">5171823</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H176">
-        <v>328</v>
+        <v>575</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516684</t>
+          <t xml:space="preserve">311516572</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,30 +10591,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 10</t>
+          <t xml:space="preserve">Stadionparken 7</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6560</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8029930</t>
+          <t xml:space="preserve">5193869</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H177">
-        <v>1471</v>
+        <v>9914</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516734</t>
+          <t xml:space="preserve">311516603</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,30 +10651,30 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 10</t>
+          <t xml:space="preserve">Stadionparken 7</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6560</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8029930</t>
+          <t xml:space="preserve">5193869, 100770346</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H178">
-        <v>1067</v>
+        <v>983</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516734</t>
+          <t xml:space="preserve">311516590</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 10</t>
+          <t xml:space="preserve">Vestermarksvej 2C</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10726,11 +10726,11 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H179">
-        <v>1504</v>
+        <v>2159</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarksvej 2C</t>
+          <t xml:space="preserve">Skolevej 52</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6560</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8029930</t>
+          <t xml:space="preserve">5187373</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>2159</v>
+        <v>272</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516734</t>
+          <t xml:space="preserve">311646458</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-29</t>
+          <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 52</t>
+          <t xml:space="preserve">Julius Nielsens Vej 33</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5187373</t>
+          <t xml:space="preserve">5193438</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,16 +10850,16 @@
         </is>
       </c>
       <c r="H181">
-        <v>272</v>
+        <v>4235</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646458</t>
+          <t xml:space="preserve">311656138</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-01-25</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,30 +10891,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olufskærvej 17</t>
+          <t xml:space="preserve">Julius Nielsens Vej 33</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035367</t>
+          <t xml:space="preserve">5193438</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H182">
-        <v>844</v>
+        <v>2630</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655998</t>
+          <t xml:space="preserve">311656140</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10951,17 +10951,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julius Nielsens Vej 33</t>
+          <t xml:space="preserve">Olufskærvej 17</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193438</t>
+          <t xml:space="preserve">100035367</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10970,11 +10970,11 @@
         </is>
       </c>
       <c r="H183">
-        <v>4235</v>
+        <v>844</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656138</t>
+          <t xml:space="preserve">311655998</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julius Nielsens Vej 33</t>
+          <t xml:space="preserve">Møllevej 24A</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5193438</t>
+          <t xml:space="preserve">5187374</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H185">
-        <v>2630</v>
+        <v>668</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656140</t>
+          <t xml:space="preserve">311658779</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-25</t>
+          <t xml:space="preserve">2033-02-08</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 24A</t>
+          <t xml:space="preserve">Rådhuscentret 7</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,25 +11201,25 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5187374</t>
+          <t xml:space="preserve">100008282</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H187">
-        <v>668</v>
+        <v>4535</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311658779</t>
+          <t xml:space="preserve">311660456</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-08</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,17 +11251,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuscentret 7</t>
+          <t xml:space="preserve">Bramdrup Vestergade 9</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">100008282</t>
+          <t xml:space="preserve">8285462</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11270,16 +11270,16 @@
         </is>
       </c>
       <c r="H188">
-        <v>4535</v>
+        <v>311</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660456</t>
+          <t xml:space="preserve">311661671</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,30 +11311,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbyvej 2</t>
+          <t xml:space="preserve">Bramdrup Vestergade 9</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5191980</t>
+          <t xml:space="preserve">8285462</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H189">
-        <v>1316</v>
+        <v>630</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713847</t>
+          <t xml:space="preserve">311661671</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bramdrup Vestergade 9</t>
+          <t xml:space="preserve">Bramdrup Vestergade 9A</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11386,15 +11386,15 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H190">
-        <v>311</v>
+        <v>1068</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661669</t>
+          <t xml:space="preserve">311661667</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,30 +11431,30 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bramdrup Vestergade 9A</t>
+          <t xml:space="preserve">Skovbyvej 2</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285462</t>
+          <t xml:space="preserve">5191980</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H191">
-        <v>1068</v>
+        <v>1316</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661669</t>
+          <t xml:space="preserve">311713847</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11491,35 +11491,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bramdrup Vestergade 9</t>
+          <t xml:space="preserve">Hammelev Bygade 18B</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100</t>
+          <t xml:space="preserve">6500</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8285462</t>
+          <t xml:space="preserve">5183526</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H192">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661669</t>
+          <t xml:space="preserve">311681008</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-03-16</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammelev Bygade 18B</t>
+          <t xml:space="preserve">Hovedgaden Øst 33</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,25 +11561,25 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5183526</t>
+          <t xml:space="preserve">5190498</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H193">
-        <v>627</v>
+        <v>836</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311681008</t>
+          <t xml:space="preserve">311713844</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-16</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11626,11 +11626,11 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H194">
-        <v>836</v>
+        <v>1680</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -11686,11 +11686,11 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H195">
-        <v>1680</v>
+        <v>2257</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden Øst 33</t>
+          <t xml:space="preserve">Skolevænget 1B</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11746,11 +11746,11 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H196">
-        <v>2257</v>
+        <v>3154</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1B</t>
+          <t xml:space="preserve">Erik Eriksens Vej 7</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11801,25 +11801,25 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5190498</t>
+          <t xml:space="preserve">5183526</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H197">
-        <v>3154</v>
+        <v>355</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713844</t>
+          <t xml:space="preserve">311681007</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-05-16</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11866,11 +11866,11 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H198">
-        <v>355</v>
+        <v>3520</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -11971,35 +11971,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erik Eriksens Vej 7</t>
+          <t xml:space="preserve">Bispegade 15</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500</t>
+          <t xml:space="preserve">6100</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5183526</t>
+          <t xml:space="preserve">306221, 306222, 306223, 306224, 306225, 306229, 306226, 306227, 306228</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H200">
-        <v>3520</v>
+        <v>8548</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311681007</t>
+          <t xml:space="preserve">311776578</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-16</t>
+          <t xml:space="preserve">2034-08-06</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">

--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -5154,7 +5154,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223881</t>
+          <t xml:space="preserve">311223876</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246904</t>
+          <t xml:space="preserve">311246892</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257671</t>
+          <t xml:space="preserve">311257761</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479972</t>
+          <t xml:space="preserve">311480076</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661671</t>
+          <t xml:space="preserve">311661669</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661671</t>
+          <t xml:space="preserve">311661669</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">

--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:M207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-23</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-30</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S (Haderslev)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-20</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-01</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-26</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-26</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-31</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Haderslev</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-05-02</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sønderjylland</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-01-10</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-27</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sønderjylland</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-15</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Center Sønderjylland</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-15</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-29</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 as</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-02-02</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 as</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-12</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-13</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-20</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5154,20 +5579,25 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223876</t>
+          <t xml:space="preserve">311223878</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5214,20 +5644,25 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311223878</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5274,20 +5709,25 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311223878</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5334,20 +5774,25 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311223878</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5394,20 +5839,25 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311223878</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5454,20 +5904,25 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223851</t>
+          <t xml:space="preserve">311223878</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-12</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-04</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-13</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-15</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7794,20 +8439,25 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7854,20 +8504,25 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8094,20 +8764,25 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8214,20 +8894,25 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8274,20 +8959,25 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-12</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-19</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Total-Tjek</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-22</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-29</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-26</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-01</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8934,20 +9674,25 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480076</t>
+          <t xml:space="preserve">311479972</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-02</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-11</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-23</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-01-22</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-04</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-04</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-04</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-23</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-28</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-28</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-01</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-25</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-25</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-25</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-25</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-08</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-08</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-16</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-16</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-16</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-16</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-06</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-08-29</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-04</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-29</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-07</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,21 +13449,26 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-22</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L207"/>
+  <autoFilter ref="A1:M207"/>
 </worksheet>
 </file>
--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -5579,7 +5579,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223876</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223878</t>
+          <t xml:space="preserve">311223851</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246892</t>
+          <t xml:space="preserve">311246886</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257761</t>
+          <t xml:space="preserve">311257671</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
